--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Konten-13b-Steuerberater.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Konten-13b-Steuerberater.xlsx
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: Inhalt seit Ihrer Freigabe geändert und/oder ohne unterschriebenes Blatt. Die Prüfsumme bestimmt die Fassung; jede Änderung ergibt eine neue.</t>
+          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu den Vorlagen liegen die aktuellen PDFs bei.</t>
+          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
